--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136042926</v>
       </c>
       <c r="B8" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136042927</v>
       </c>
       <c r="B9" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20941-2026 artfynd.xlsx
+++ b/artfynd/A 20941-2026 artfynd.xlsx
@@ -1440,7 +1440,7 @@
         <v>136042926</v>
       </c>
       <c r="B8" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136042927</v>
       </c>
       <c r="B9" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
